--- a/data/session.xlsx
+++ b/data/session.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +433,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="1" t="n">
+        <v>46096.02828432495</v>
+      </c>
       <c r="B2" t="inlineStr"/>
     </row>
   </sheetData>
